--- a/ROSA_vitaSPEC/Results/test_pretraitements/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.3730231177627215</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.5092537447197971</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.5695083235523322</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.6016732381960563</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.650550287309365</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.6831045404663534</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.7169233050808261</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.7280989209011428</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.7466675665366539</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.7585986707038195</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.7740278304988016</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.7890138144061607</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.8103013388048651</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.8296987430902329</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.8369753935476326</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.4168563990200836</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.508264774459575</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.5366850383810763</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.6102448570143126</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.6703783880489147</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.6824535698281102</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.7045065602706011</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.7314836798115074</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.7537900953874973</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.7787764334505006</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.8055508981094162</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8336048152310357</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.866108059816896</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8823692560111186</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8920336160437876</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.3817797895632762</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.478925177829427</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.502174345591804</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.5802267970872068</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.6380002007838113</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.6752809200657353</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.6875072806951018</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.702418943059069</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.7317634281281107</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.7553618677978574</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.7690754041985616</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.7930318014227964</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.8108589871567519</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.8250936721644009</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.8452919690861993</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.4908644850697281</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.524007869203475</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.5690889542188065</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.6104903735925959</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.6729825760779491</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.6941857492846137</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.7062822002234093</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.7258478400937953</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.754953831175885</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.7800478265556989</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.800581940093575</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.8249109247633405</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.8433952367518055</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8601892086123619</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.8790802423705871</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.4901750166816692</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.5228488664048816</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.569720564696422</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.6131245430135829</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.6693228940941589</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.6854759257116112</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.7037506906786337</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.727758594821856</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.7533017739405361</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.765671891248782</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.7902788951729292</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.8141434227211789</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8328165573184538</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8461642170100347</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8657229050043299</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.3827238950345615</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.4993615741876161</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.6050042032174393</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.6268415609151494</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.6747230501293084</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.6916472930560975</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.7171521605833686</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.7330875664966966</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.7473728885382536</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.7724708394504062</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.7902363424549836</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.8017868058471243</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.8195429647061727</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.8353480372443953</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.8505532145601737</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.422695887876732</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.4828300331657643</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.5993406694635905</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.6449067253957107</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.6604182398296787</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.7051835947668574</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.7181278306125823</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.7284997761709013</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.7440873505234101</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.7663518622636156</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.7780215078236383</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.789872286453944</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8056920686046583</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.8277103844473008</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.8386102531043025</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.4226635978778882</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.482773298106828</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.5986447653388102</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.6423688335346369</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.6564821241463881</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.6982657050747052</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.7094170313823012</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.7175462420871977</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.7232731298928272</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.730914211047924</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.7360617903062858</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.741886017496578</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.7535617249793981</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.7662750572420918</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.7713391185530786</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.4226321929543297</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.4827621303728091</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.5986187884468148</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.6422631916381796</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.6562870740054449</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.6978878550174192</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.7090431141882645</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.7169322645873999</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.7224813717730572</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.7295782250337153</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.734400466278643</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.7394135980539627</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.7480547501390906</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.7593962167937789</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.7641649031521123</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.4226639787456897</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.4827611612048947</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.5988107097056909</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.642887860487234</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.6569922612916401</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.6974994502058341</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.7078347909701701</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.7165872873652739</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.7225890798055306</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.7313857683589335</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.7370241938622788</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.7439672931192927</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.7523232634911013</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.7631474677475624</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.767020048861455</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.5056542699412008</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.5637894515611076</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.6104318546509842</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.6476848932952022</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.7062807229172374</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.7216209810212315</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.7360487186739182</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.7464303985398605</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.7615918822628109</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.7802917931819437</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.794320581759455</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.8116680330721172</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.8233207360284406</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.8416551670707955</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8572811429544192</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.5061794997925799</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.5867247977061372</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.6260739854231735</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.6855944690370456</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.715958146829296</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.7295739124639598</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.7414295300356796</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.754887212636135</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.7759774173255116</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.7931535348343761</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.8043444427976103</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.8142733625543622</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8290958058773548</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.8422685488994167</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.855669096776936</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.3827164485773433</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.4993252264696374</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.6048013703741737</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.6264895689734571</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.6732253588595712</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.6891436009496799</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.7125457105843055</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.727113579846546</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.7392183816634409</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.7549565335331481</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.7650170194462982</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.770577812446204</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.781568215272435</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.7874306736271522</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.794215747577065</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.3826947904097223</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.4993192152422692</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.6047716567808408</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.6264586782442407</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.6731649233174868</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.6890711643453662</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.7122695965364634</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.7264816427039518</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.7379227310206171</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.7515070002605998</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.7593341076305166</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.7637638087411214</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.7771177874752286</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.7833709686984724</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.7867860493021164</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.3826680375395182</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.4993162167170011</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.604719454166283</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.6264080416524795</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.6730923685394615</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.6890031942066235</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.712183703556585</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.7265523032865372</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.7380274525825261</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.7503623651535831</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.7572001357044822</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.7603424303221942</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.7713423206196074</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.7784739098635068</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.7817416736028479</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.3826020005044561</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.4993040314591466</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.60460946334509</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.626299164816419</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.672817503921427</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.6887072308999387</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.7116823698485508</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.7262981431126856</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.7383067722360539</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7501295322147055</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.7565151992934707</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.7590376902330177</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.7673984210505722</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.7738669195963723</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.7772548132842918</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.5064748961941843</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.5616132436032</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.604326356251112</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.6421700642456684</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.6968033742504702</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.7292592704580964</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.736885246310822</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.7479499848967266</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.770576758648756</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.7937728987546018</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.8122492019211041</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.8374114186104323</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8515341136898193</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.8668385435260753</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.8829477535715274</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.5058569455648595</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.5627511831419318</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.6060924207304899</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.646232627486389</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.6864160398639172</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.7099675665468074</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.7243049118966116</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.7492291068836745</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.7673460448542528</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.7804267916189631</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.8029966004361384</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.8193350605683609</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.8331858160958814</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8472566118160794</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8645797921952081</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.5058171280915551</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.5615350083348347</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.6024771822741593</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.6723641719898574</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.6859734004923934</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.7077319915306441</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.714861980028894</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.7447198077051165</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.7573491818615047</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.7684640857229542</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.7869870182198351</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.7998840400683355</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.8103004155800686</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8260671216219903</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8420850024820479</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.4152869273065005</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.5052846058893385</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.531776494890698</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.6202743577261074</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.6402380763576108</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.6579713478425738</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.7022558872865428</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.7366725879216119</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.7576708132738321</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.8023523655788352</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.8185192249175152</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8424500889582598</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.870768244243848</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.8837737902371493</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.8942218497966122</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.4140331305619007</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.5044247879877184</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.5277096927262315</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.6208131535411036</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.6405742776076935</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.6551433971067047</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.7029419708448175</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.7374111163281903</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.7617554809394533</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.7927171561286436</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.8226350824229239</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.858841912578801</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.876168291032186</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8859565467132231</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.8976043189242136</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.5015564576312628</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.5181653155430166</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.5667411363577106</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.583012540238807</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.6487611641003932</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.6880945121153779</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.7278555563170808</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7686053690180525</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.7785958546060282</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8117065405955006</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8495126698033431</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.862502703574997</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8785856554990542</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.897209233307775</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9137405072091715</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.2381259911379071</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.3499815656272283</v>
+        <v>0.536534807297029</v>
       </c>
       <c r="D24">
-        <v>0.3717995688914817</v>
+        <v>0.5727383740030878</v>
       </c>
       <c r="E24">
-        <v>0.4009916944145533</v>
+        <v>0.6013648345886283</v>
       </c>
       <c r="F24">
-        <v>0.5103319361224167</v>
+        <v>0.61969534535147</v>
       </c>
       <c r="G24">
-        <v>0.5433826252900102</v>
+        <v>0.6544084771953788</v>
       </c>
       <c r="H24">
-        <v>0.6003437980896986</v>
+        <v>0.6803517736770353</v>
       </c>
       <c r="I24">
-        <v>0.6386701955734742</v>
+        <v>0.6922922291631606</v>
       </c>
       <c r="J24">
-        <v>0.679762247481134</v>
+        <v>0.7317534117838609</v>
       </c>
       <c r="K24">
-        <v>0.7194889076730997</v>
+        <v>0.7634299604964973</v>
       </c>
       <c r="L24">
-        <v>0.7520770970370529</v>
+        <v>0.8041786940740521</v>
       </c>
       <c r="M24">
-        <v>0.7743127328659025</v>
+        <v>0.8359291833170532</v>
       </c>
       <c r="N24">
-        <v>0.8214442151643553</v>
+        <v>0.8733208875305917</v>
       </c>
       <c r="O24">
-        <v>0.8481104661096138</v>
+        <v>0.8870751837654065</v>
       </c>
       <c r="P24">
-        <v>0.8648737759546523</v>
+        <v>0.9059325041552309</v>
+      </c>
+      <c r="Q24">
+        <v>0.9176860608782953</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.2263337003997875</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.320324891687785</v>
+        <v>0.5377544003881296</v>
       </c>
       <c r="D25">
-        <v>0.3540144499922362</v>
+        <v>0.57686337792857</v>
       </c>
       <c r="E25">
-        <v>0.4492305809186855</v>
+        <v>0.62386694488455</v>
       </c>
       <c r="F25">
-        <v>0.5097342226214132</v>
+        <v>0.6482801439427706</v>
       </c>
       <c r="G25">
-        <v>0.5417998392888305</v>
+        <v>0.6815563422455561</v>
       </c>
       <c r="H25">
-        <v>0.5863849126348865</v>
+        <v>0.7019346705989618</v>
       </c>
       <c r="I25">
-        <v>0.629041258248128</v>
+        <v>0.7098136550724401</v>
       </c>
       <c r="J25">
-        <v>0.6691020994325607</v>
+        <v>0.7570045091097107</v>
       </c>
       <c r="K25">
-        <v>0.7080774060572889</v>
+        <v>0.7713029743756186</v>
       </c>
       <c r="L25">
-        <v>0.7510699777180911</v>
+        <v>0.8229392395006696</v>
       </c>
       <c r="M25">
-        <v>0.7967472154180824</v>
+        <v>0.8519370822417848</v>
       </c>
       <c r="N25">
-        <v>0.8254041407485553</v>
+        <v>0.8637145586291939</v>
       </c>
       <c r="O25">
-        <v>0.8441414273667688</v>
+        <v>0.8902757771692928</v>
       </c>
       <c r="P25">
-        <v>0.8704084490960101</v>
+        <v>0.9052305920828276</v>
+      </c>
+      <c r="Q25">
+        <v>0.9153350373426956</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.2074237165548901</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.3261227027574621</v>
+        <v>0.5503078107873829</v>
       </c>
       <c r="D26">
-        <v>0.344560944072633</v>
+        <v>0.5699375525021959</v>
       </c>
       <c r="E26">
-        <v>0.3770105003078655</v>
+        <v>0.6275210486744521</v>
       </c>
       <c r="F26">
-        <v>0.4236966027934908</v>
+        <v>0.6581790191648829</v>
       </c>
       <c r="G26">
-        <v>0.4449098199714878</v>
+        <v>0.6825052759326709</v>
       </c>
       <c r="H26">
-        <v>0.4767410191516891</v>
+        <v>0.700176538351734</v>
       </c>
       <c r="I26">
-        <v>0.5064625325024499</v>
+        <v>0.7162642901312545</v>
       </c>
       <c r="J26">
-        <v>0.5361731274319655</v>
+        <v>0.7457546360888223</v>
       </c>
       <c r="K26">
-        <v>0.5643990609585736</v>
+        <v>0.7981670832696112</v>
       </c>
       <c r="L26">
-        <v>0.5975353315480418</v>
+        <v>0.8294560595999381</v>
       </c>
       <c r="M26">
-        <v>0.6211844039480118</v>
+        <v>0.8563298543176332</v>
       </c>
       <c r="N26">
-        <v>0.6548565019481132</v>
+        <v>0.8871692422104868</v>
       </c>
       <c r="O26">
-        <v>0.6975687186153353</v>
+        <v>0.9061185514340767</v>
       </c>
       <c r="P26">
-        <v>0.7176432319033477</v>
+        <v>0.9154235773723296</v>
+      </c>
+      <c r="Q26">
+        <v>0.927776748388856</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.181592093100001</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.2615803433588111</v>
+        <v>0.5502483960999583</v>
       </c>
       <c r="D27">
-        <v>0.4043733423728674</v>
+        <v>0.5696890950943203</v>
       </c>
       <c r="E27">
-        <v>0.4139286604699118</v>
+        <v>0.6265327254030726</v>
       </c>
       <c r="F27">
-        <v>0.455797203140249</v>
+        <v>0.6561598441239092</v>
       </c>
       <c r="G27">
-        <v>0.4972494045449236</v>
+        <v>0.6790623554335096</v>
       </c>
       <c r="H27">
-        <v>0.5215406946082728</v>
+        <v>0.6939937031433562</v>
       </c>
       <c r="I27">
-        <v>0.5621498615685683</v>
+        <v>0.7043074709651902</v>
       </c>
       <c r="J27">
-        <v>0.6109945694181576</v>
+        <v>0.7217281626511942</v>
       </c>
       <c r="K27">
-        <v>0.6314027956398813</v>
+        <v>0.7470605358818503</v>
       </c>
       <c r="L27">
-        <v>0.6512305829531801</v>
+        <v>0.7590503916957279</v>
       </c>
       <c r="M27">
-        <v>0.703295181110108</v>
+        <v>0.7667824463805153</v>
       </c>
       <c r="N27">
-        <v>0.7209173916598424</v>
+        <v>0.7816535429622474</v>
       </c>
       <c r="O27">
-        <v>0.7661882039804087</v>
+        <v>0.7884066962603157</v>
       </c>
       <c r="P27">
-        <v>0.7747403617291508</v>
+        <v>0.7994767754161731</v>
+      </c>
+      <c r="Q27">
+        <v>0.8086466492343534</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.536534807297029</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.5727383740030878</v>
+        <v>0.5376624118370573</v>
       </c>
       <c r="D28">
-        <v>0.6013648345886283</v>
+        <v>0.5767156396830249</v>
       </c>
       <c r="E28">
-        <v>0.61969534535147</v>
+        <v>0.623138502004094</v>
       </c>
       <c r="F28">
-        <v>0.6544084771953788</v>
+        <v>0.6473850248835802</v>
       </c>
       <c r="G28">
-        <v>0.6803517736770353</v>
+        <v>0.6794602761961031</v>
       </c>
       <c r="H28">
-        <v>0.6922922291631606</v>
+        <v>0.6968625703704042</v>
       </c>
       <c r="I28">
-        <v>0.7317534117838609</v>
+        <v>0.7013919704124452</v>
       </c>
       <c r="J28">
-        <v>0.7634299604964973</v>
+        <v>0.7324163707391199</v>
       </c>
       <c r="K28">
-        <v>0.8041786940740521</v>
+        <v>0.7409024427141393</v>
       </c>
       <c r="L28">
-        <v>0.8359291833170532</v>
+        <v>0.7704208245995987</v>
       </c>
       <c r="M28">
-        <v>0.8733208875305917</v>
+        <v>0.7779020039770145</v>
       </c>
       <c r="N28">
-        <v>0.8870751837654065</v>
+        <v>0.7850719832651475</v>
       </c>
       <c r="O28">
-        <v>0.9059325041552309</v>
+        <v>0.7927490586596336</v>
       </c>
       <c r="P28">
-        <v>0.9176860608782953</v>
+        <v>0.7966085935825793</v>
+      </c>
+      <c r="Q28">
+        <v>0.8075693810671406</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.5377544003881296</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.57686337792857</v>
+        <v>0.5375758430481767</v>
       </c>
       <c r="D29">
-        <v>0.62386694488455</v>
+        <v>0.5766684022197544</v>
       </c>
       <c r="E29">
-        <v>0.6482801439427706</v>
+        <v>0.6229412903993981</v>
       </c>
       <c r="F29">
-        <v>0.6815563422455561</v>
+        <v>0.6473358682032145</v>
       </c>
       <c r="G29">
-        <v>0.7019346705989618</v>
+        <v>0.6793290663478412</v>
       </c>
       <c r="H29">
-        <v>0.7098136550724401</v>
+        <v>0.6965303807153989</v>
       </c>
       <c r="I29">
-        <v>0.7570045091097107</v>
+        <v>0.7008573409721425</v>
       </c>
       <c r="J29">
-        <v>0.7713029743756186</v>
+        <v>0.7306555794680943</v>
       </c>
       <c r="K29">
-        <v>0.8229392395006696</v>
+        <v>0.7394095510386487</v>
       </c>
       <c r="L29">
-        <v>0.8519370822417848</v>
+        <v>0.7680942324555446</v>
       </c>
       <c r="M29">
-        <v>0.8637145586291939</v>
+        <v>0.7742344684719904</v>
       </c>
       <c r="N29">
-        <v>0.8902757771692928</v>
+        <v>0.7828156438570815</v>
       </c>
       <c r="O29">
-        <v>0.9052305920828276</v>
+        <v>0.7891501426328988</v>
       </c>
       <c r="P29">
-        <v>0.9153350373426956</v>
+        <v>0.792012523302832</v>
+      </c>
+      <c r="Q29">
+        <v>0.8005426542211873</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.5503078107873829</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.5699375525021959</v>
+        <v>0.5375194062927739</v>
       </c>
       <c r="D30">
-        <v>0.6275210486744521</v>
+        <v>0.5766494775154374</v>
       </c>
       <c r="E30">
-        <v>0.6581790191648829</v>
+        <v>0.6227854433991966</v>
       </c>
       <c r="F30">
-        <v>0.6825052759326709</v>
+        <v>0.6472556008079599</v>
       </c>
       <c r="G30">
-        <v>0.700176538351734</v>
+        <v>0.6792070655519551</v>
       </c>
       <c r="H30">
-        <v>0.7162642901312545</v>
+        <v>0.6962962515178843</v>
       </c>
       <c r="I30">
-        <v>0.7457546360888223</v>
+        <v>0.7005081390152365</v>
       </c>
       <c r="J30">
-        <v>0.7981670832696112</v>
+        <v>0.7295923479113569</v>
       </c>
       <c r="K30">
-        <v>0.8294560595999381</v>
+        <v>0.7385446534973277</v>
       </c>
       <c r="L30">
-        <v>0.8563298543176332</v>
+        <v>0.7667450109583414</v>
       </c>
       <c r="M30">
-        <v>0.8871692422104868</v>
+        <v>0.7723267460690977</v>
       </c>
       <c r="N30">
-        <v>0.9061185514340767</v>
+        <v>0.7814113625870696</v>
       </c>
       <c r="O30">
-        <v>0.9154235773723296</v>
+        <v>0.7870959256526691</v>
       </c>
       <c r="P30">
-        <v>0.927776748388856</v>
+        <v>0.7897025643941643</v>
+      </c>
+      <c r="Q30">
+        <v>0.7971032130287289</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.5502483960999583</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.5696890950943203</v>
+        <v>0.5373688339229091</v>
       </c>
       <c r="D31">
-        <v>0.6265327254030726</v>
+        <v>0.5765759137468116</v>
       </c>
       <c r="E31">
-        <v>0.6561598441239092</v>
+        <v>0.6224663107041793</v>
       </c>
       <c r="F31">
-        <v>0.6790623554335096</v>
+        <v>0.6471864449124249</v>
       </c>
       <c r="G31">
-        <v>0.6939937031433562</v>
+        <v>0.6791677761161953</v>
       </c>
       <c r="H31">
-        <v>0.7043074709651902</v>
+        <v>0.6961407985649319</v>
       </c>
       <c r="I31">
-        <v>0.7217281626511942</v>
+        <v>0.7001929718969075</v>
       </c>
       <c r="J31">
-        <v>0.7470605358818503</v>
+        <v>0.7279666203979926</v>
       </c>
       <c r="K31">
-        <v>0.7590503916957279</v>
+        <v>0.7375803513551404</v>
       </c>
       <c r="L31">
-        <v>0.7667824463805153</v>
+        <v>0.7655509255449653</v>
       </c>
       <c r="M31">
-        <v>0.7816535429622474</v>
+        <v>0.7710381244543607</v>
       </c>
       <c r="N31">
-        <v>0.7884066962603157</v>
+        <v>0.7803810446288145</v>
       </c>
       <c r="O31">
-        <v>0.7994767754161731</v>
+        <v>0.7849661122723737</v>
       </c>
       <c r="P31">
-        <v>0.8086466492343534</v>
+        <v>0.7872775403921877</v>
+      </c>
+      <c r="Q31">
+        <v>0.7927306051451299</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.5376624118370573</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.5767156396830249</v>
+        <v>0.5377310014445054</v>
       </c>
       <c r="D32">
-        <v>0.623138502004094</v>
+        <v>0.576760174549414</v>
       </c>
       <c r="E32">
-        <v>0.6473850248835802</v>
+        <v>0.6233251347229759</v>
       </c>
       <c r="F32">
-        <v>0.6794602761961031</v>
+        <v>0.6474670010905044</v>
       </c>
       <c r="G32">
-        <v>0.6968625703704042</v>
+        <v>0.6796447521509428</v>
       </c>
       <c r="H32">
-        <v>0.7013919704124452</v>
+        <v>0.697328259611312</v>
       </c>
       <c r="I32">
-        <v>0.7324163707391199</v>
+        <v>0.7022137483149731</v>
       </c>
       <c r="J32">
-        <v>0.7409024427141393</v>
+        <v>0.734739668433725</v>
       </c>
       <c r="K32">
-        <v>0.7704208245995987</v>
+        <v>0.7434381491175561</v>
       </c>
       <c r="L32">
-        <v>0.7779020039770145</v>
+        <v>0.7770047183358088</v>
       </c>
       <c r="M32">
-        <v>0.7850719832651475</v>
+        <v>0.7892098077262157</v>
       </c>
       <c r="N32">
-        <v>0.7927490586596336</v>
+        <v>0.7977202944889936</v>
       </c>
       <c r="O32">
-        <v>0.7966085935825793</v>
+        <v>0.8155886384671479</v>
       </c>
       <c r="P32">
-        <v>0.8075693810671406</v>
+        <v>0.821480185990535</v>
+      </c>
+      <c r="Q32">
+        <v>0.8346317312466198</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.5375758430481767</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.5766684022197544</v>
+        <v>0.537714412998107</v>
       </c>
       <c r="D33">
-        <v>0.6229412903993981</v>
+        <v>0.5767487465485626</v>
       </c>
       <c r="E33">
-        <v>0.6473358682032145</v>
+        <v>0.6232791060105725</v>
       </c>
       <c r="F33">
-        <v>0.6793290663478412</v>
+        <v>0.647444139142649</v>
       </c>
       <c r="G33">
-        <v>0.6965303807153989</v>
+        <v>0.6795927433283203</v>
       </c>
       <c r="H33">
-        <v>0.7008573409721425</v>
+        <v>0.6971901176667346</v>
       </c>
       <c r="I33">
-        <v>0.7306555794680943</v>
+        <v>0.7020005618615019</v>
       </c>
       <c r="J33">
-        <v>0.7394095510386487</v>
+        <v>0.7339991875244185</v>
       </c>
       <c r="K33">
-        <v>0.7680942324555446</v>
+        <v>0.7425646344722041</v>
       </c>
       <c r="L33">
-        <v>0.7742344684719904</v>
+        <v>0.7746175619740978</v>
       </c>
       <c r="M33">
-        <v>0.7828156438570815</v>
+        <v>0.7854873772266608</v>
       </c>
       <c r="N33">
-        <v>0.7891501426328988</v>
+        <v>0.7938289823693409</v>
       </c>
       <c r="O33">
-        <v>0.792012523302832</v>
+        <v>0.809959539857171</v>
       </c>
       <c r="P33">
-        <v>0.8005426542211873</v>
+        <v>0.8150329433747145</v>
+      </c>
+      <c r="Q33">
+        <v>0.8264111310251894</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.5375194062927739</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.5766494775154374</v>
+        <v>0.5376917162931327</v>
       </c>
       <c r="D34">
-        <v>0.6227854433991966</v>
+        <v>0.5767349248485398</v>
       </c>
       <c r="E34">
-        <v>0.6472556008079599</v>
+        <v>0.6232044768330189</v>
       </c>
       <c r="F34">
-        <v>0.6792070655519551</v>
+        <v>0.6474083970936293</v>
       </c>
       <c r="G34">
-        <v>0.6962962515178843</v>
+        <v>0.6795166316072464</v>
       </c>
       <c r="H34">
-        <v>0.7005081390152365</v>
+        <v>0.6970215362128438</v>
       </c>
       <c r="I34">
-        <v>0.7295923479113569</v>
+        <v>0.7017255344139476</v>
       </c>
       <c r="J34">
-        <v>0.7385446534973277</v>
+        <v>0.7330132117119827</v>
       </c>
       <c r="K34">
-        <v>0.7667450109583414</v>
+        <v>0.7414847538541183</v>
       </c>
       <c r="L34">
-        <v>0.7723267460690977</v>
+        <v>0.7716395471494972</v>
       </c>
       <c r="M34">
-        <v>0.7814113625870696</v>
+        <v>0.781090017958819</v>
       </c>
       <c r="N34">
-        <v>0.7870959256526691</v>
+        <v>0.7898934985138581</v>
       </c>
       <c r="O34">
-        <v>0.7897025643941643</v>
+        <v>0.8056616826316627</v>
       </c>
       <c r="P34">
-        <v>0.7971032130287289</v>
+        <v>0.8113945806576001</v>
+      </c>
+      <c r="Q34">
+        <v>0.8190043238119901</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.5373688339229091</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.5765759137468116</v>
+        <v>0.5376615431775735</v>
       </c>
       <c r="D35">
-        <v>0.6224663107041793</v>
+        <v>0.5767177323807924</v>
       </c>
       <c r="E35">
-        <v>0.6471864449124249</v>
+        <v>0.6231090541331867</v>
       </c>
       <c r="F35">
-        <v>0.6791677761161953</v>
+        <v>0.6473777685101225</v>
       </c>
       <c r="G35">
-        <v>0.6961407985649319</v>
+        <v>0.6794805218513538</v>
       </c>
       <c r="H35">
-        <v>0.7001929718969075</v>
+        <v>0.6969496574854623</v>
       </c>
       <c r="I35">
-        <v>0.7279666203979926</v>
+        <v>0.701582477791121</v>
       </c>
       <c r="J35">
-        <v>0.7375803513551404</v>
+        <v>0.7321086568402575</v>
       </c>
       <c r="K35">
-        <v>0.7655509255449653</v>
+        <v>0.7404946587383114</v>
       </c>
       <c r="L35">
-        <v>0.7710381244543607</v>
+        <v>0.7686299373968903</v>
       </c>
       <c r="M35">
-        <v>0.7803810446288145</v>
+        <v>0.7756848480357696</v>
       </c>
       <c r="N35">
-        <v>0.7849661122723737</v>
+        <v>0.7843049412446882</v>
       </c>
       <c r="O35">
-        <v>0.7872775403921877</v>
+        <v>0.7983028151319954</v>
       </c>
       <c r="P35">
-        <v>0.7927306051451299</v>
+        <v>0.803590125848981</v>
+      </c>
+      <c r="Q35">
+        <v>0.8107149819526698</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.5377310014445054</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.576760174549414</v>
+        <v>0.5373682188664093</v>
       </c>
       <c r="D36">
-        <v>0.6233251347229759</v>
+        <v>0.5765799825773692</v>
       </c>
       <c r="E36">
-        <v>0.6474670010905044</v>
+        <v>0.6223907227379052</v>
       </c>
       <c r="F36">
-        <v>0.6796447521509428</v>
+        <v>0.6472123766319786</v>
       </c>
       <c r="G36">
-        <v>0.697328259611312</v>
+        <v>0.6793364263675226</v>
       </c>
       <c r="H36">
-        <v>0.7022137483149731</v>
+        <v>0.6965228327193544</v>
       </c>
       <c r="I36">
-        <v>0.734739668433725</v>
+        <v>0.7007175106984773</v>
       </c>
       <c r="J36">
-        <v>0.7434381491175561</v>
+        <v>0.7283615913468444</v>
       </c>
       <c r="K36">
-        <v>0.7770047183358088</v>
+        <v>0.7380607647778989</v>
       </c>
       <c r="L36">
-        <v>0.7892098077262157</v>
+        <v>0.7652809572758572</v>
       </c>
       <c r="M36">
-        <v>0.7977202944889936</v>
+        <v>0.7714064209037274</v>
       </c>
       <c r="N36">
-        <v>0.8155886384671479</v>
+        <v>0.7801738857327633</v>
       </c>
       <c r="O36">
-        <v>0.821480185990535</v>
+        <v>0.7862100523054523</v>
       </c>
       <c r="P36">
-        <v>0.8346317312466198</v>
+        <v>0.7881286230189394</v>
+      </c>
+      <c r="Q36">
+        <v>0.7921946713945991</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.537714412998107</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.5767487465485626</v>
+        <v>0.556814187999634</v>
       </c>
       <c r="D37">
-        <v>0.6232791060105725</v>
+        <v>0.5862212107865146</v>
       </c>
       <c r="E37">
-        <v>0.647444139142649</v>
+        <v>0.6380303588217435</v>
       </c>
       <c r="F37">
-        <v>0.6795927433283203</v>
+        <v>0.6611654900114639</v>
       </c>
       <c r="G37">
-        <v>0.6971901176667346</v>
+        <v>0.6983892078323231</v>
       </c>
       <c r="H37">
-        <v>0.7020005618615019</v>
+        <v>0.7524635915942648</v>
       </c>
       <c r="I37">
-        <v>0.7339991875244185</v>
+        <v>0.7835475814039483</v>
       </c>
       <c r="J37">
-        <v>0.7425646344722041</v>
+        <v>0.8115775040785567</v>
       </c>
       <c r="K37">
-        <v>0.7746175619740978</v>
+        <v>0.8212901011095481</v>
       </c>
       <c r="L37">
-        <v>0.7854873772266608</v>
+        <v>0.848075423905896</v>
       </c>
       <c r="M37">
-        <v>0.7938289823693409</v>
+        <v>0.8604875848993399</v>
       </c>
       <c r="N37">
-        <v>0.809959539857171</v>
+        <v>0.8700681224338901</v>
       </c>
       <c r="O37">
-        <v>0.8150329433747145</v>
+        <v>0.8871523384716509</v>
       </c>
       <c r="P37">
-        <v>0.8264111310251894</v>
+        <v>0.9006350767528284</v>
+      </c>
+      <c r="Q37">
+        <v>0.9069129295285535</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.5376917162931327</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.5767349248485398</v>
+        <v>0.5562563947390828</v>
       </c>
       <c r="D38">
-        <v>0.6232044768330189</v>
+        <v>0.5842444191717346</v>
       </c>
       <c r="E38">
-        <v>0.6474083970936293</v>
+        <v>0.6299855042530953</v>
       </c>
       <c r="F38">
-        <v>0.6795166316072464</v>
+        <v>0.6478143421880116</v>
       </c>
       <c r="G38">
-        <v>0.6970215362128438</v>
+        <v>0.6676262724599074</v>
       </c>
       <c r="H38">
-        <v>0.7017255344139476</v>
+        <v>0.7029545591228838</v>
       </c>
       <c r="I38">
-        <v>0.7330132117119827</v>
+        <v>0.729129208921893</v>
       </c>
       <c r="J38">
-        <v>0.7414847538541183</v>
+        <v>0.7520275359447445</v>
       </c>
       <c r="K38">
-        <v>0.7716395471494972</v>
+        <v>0.7775710672717506</v>
       </c>
       <c r="L38">
-        <v>0.781090017958819</v>
+        <v>0.7975315949943416</v>
       </c>
       <c r="M38">
-        <v>0.7898934985138581</v>
+        <v>0.8060856582100233</v>
       </c>
       <c r="N38">
-        <v>0.8056616826316627</v>
+        <v>0.8328871819944875</v>
       </c>
       <c r="O38">
-        <v>0.8113945806576001</v>
+        <v>0.8628478223642969</v>
       </c>
       <c r="P38">
-        <v>0.8190043238119901</v>
+        <v>0.8761134836462897</v>
+      </c>
+      <c r="Q38">
+        <v>0.8840140112671931</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.5376615431775735</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.5767177323807924</v>
+        <v>0.556349299990362</v>
       </c>
       <c r="D39">
-        <v>0.6231090541331867</v>
+        <v>0.5845858200983682</v>
       </c>
       <c r="E39">
-        <v>0.6473777685101225</v>
+        <v>0.6281925604511666</v>
       </c>
       <c r="F39">
-        <v>0.6794805218513538</v>
+        <v>0.6474645222138913</v>
       </c>
       <c r="G39">
-        <v>0.6969496574854623</v>
+        <v>0.6658508164698665</v>
       </c>
       <c r="H39">
-        <v>0.701582477791121</v>
+        <v>0.6953729801895252</v>
       </c>
       <c r="I39">
-        <v>0.7321086568402575</v>
+        <v>0.7165363894541938</v>
       </c>
       <c r="J39">
-        <v>0.7404946587383114</v>
+        <v>0.7287428517150074</v>
       </c>
       <c r="K39">
-        <v>0.7686299373968903</v>
+        <v>0.7635126472630993</v>
       </c>
       <c r="L39">
-        <v>0.7756848480357696</v>
+        <v>0.7766894445307863</v>
       </c>
       <c r="M39">
-        <v>0.7843049412446882</v>
+        <v>0.782018497856882</v>
       </c>
       <c r="N39">
-        <v>0.7983028151319954</v>
+        <v>0.811204774603369</v>
       </c>
       <c r="O39">
-        <v>0.803590125848981</v>
+        <v>0.828298328223347</v>
       </c>
       <c r="P39">
-        <v>0.8107149819526698</v>
+        <v>0.8466015729659361</v>
+      </c>
+      <c r="Q39">
+        <v>0.866029547922833</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.5373682188664093</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.5765799825773692</v>
+        <v>0.531142077332986</v>
       </c>
       <c r="D40">
-        <v>0.6223907227379052</v>
+        <v>0.5534661866022449</v>
       </c>
       <c r="E40">
-        <v>0.6472123766319786</v>
+        <v>0.56698701370099</v>
       </c>
       <c r="F40">
-        <v>0.6793364263675226</v>
+        <v>0.620031778981365</v>
       </c>
       <c r="G40">
-        <v>0.6965228327193544</v>
+        <v>0.6594245855709158</v>
       </c>
       <c r="H40">
-        <v>0.7007175106984773</v>
+        <v>0.6909765771796053</v>
       </c>
       <c r="I40">
-        <v>0.7283615913468444</v>
+        <v>0.7133001550590943</v>
       </c>
       <c r="J40">
-        <v>0.7380607647778989</v>
+        <v>0.7323003253819161</v>
       </c>
       <c r="K40">
-        <v>0.7652809572758572</v>
+        <v>0.7528935564384555</v>
       </c>
       <c r="L40">
-        <v>0.7714064209037274</v>
+        <v>0.7724191995604216</v>
       </c>
       <c r="M40">
-        <v>0.7801738857327633</v>
+        <v>0.7930854445257278</v>
       </c>
       <c r="N40">
-        <v>0.7862100523054523</v>
+        <v>0.8190442501469444</v>
       </c>
       <c r="O40">
-        <v>0.7881286230189394</v>
+        <v>0.8532169003610808</v>
       </c>
       <c r="P40">
-        <v>0.7921946713945991</v>
+        <v>0.8766378977418169</v>
+      </c>
+      <c r="Q40">
+        <v>0.893204761640541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.556814187999634</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.5862212107865146</v>
+        <v>0.523028316214328</v>
       </c>
       <c r="D41">
-        <v>0.6380303588217435</v>
+        <v>0.5778310138275996</v>
       </c>
       <c r="E41">
-        <v>0.6611654900114639</v>
+        <v>0.6199097189934275</v>
       </c>
       <c r="F41">
-        <v>0.6983892078323231</v>
+        <v>0.6733652558540062</v>
       </c>
       <c r="G41">
-        <v>0.7524635915942648</v>
+        <v>0.7225831599567458</v>
       </c>
       <c r="H41">
-        <v>0.7835475814039483</v>
+        <v>0.7532819788865696</v>
       </c>
       <c r="I41">
-        <v>0.8115775040785567</v>
+        <v>0.7864096176910289</v>
       </c>
       <c r="J41">
-        <v>0.8212901011095481</v>
+        <v>0.8077801568330422</v>
       </c>
       <c r="K41">
-        <v>0.848075423905896</v>
+        <v>0.8239796265922745</v>
       </c>
       <c r="L41">
-        <v>0.8604875848993399</v>
+        <v>0.8427766467483349</v>
       </c>
       <c r="M41">
-        <v>0.8700681224338901</v>
+        <v>0.8687206319824909</v>
       </c>
       <c r="N41">
-        <v>0.8871523384716509</v>
+        <v>0.8954189132756132</v>
       </c>
       <c r="O41">
-        <v>0.9006350767528284</v>
+        <v>0.9132506057882768</v>
       </c>
       <c r="P41">
-        <v>0.9069129295285535</v>
+        <v>0.9289566971746739</v>
+      </c>
+      <c r="Q41">
+        <v>0.9378009314809052</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.5562563947390828</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.5842444191717346</v>
+        <v>0.4367333784920707</v>
       </c>
       <c r="D42">
-        <v>0.6299855042530953</v>
+        <v>0.5425429154744063</v>
       </c>
       <c r="E42">
-        <v>0.6478143421880116</v>
+        <v>0.5771025558699054</v>
       </c>
       <c r="F42">
-        <v>0.6676262724599074</v>
+        <v>0.6392933696490982</v>
       </c>
       <c r="G42">
-        <v>0.7029545591228838</v>
+        <v>0.6857360884758095</v>
       </c>
       <c r="H42">
-        <v>0.729129208921893</v>
+        <v>0.7092763137276223</v>
       </c>
       <c r="I42">
-        <v>0.7520275359447445</v>
+        <v>0.7344243403473428</v>
       </c>
       <c r="J42">
-        <v>0.7775710672717506</v>
+        <v>0.747344570129066</v>
       </c>
       <c r="K42">
-        <v>0.7975315949943416</v>
+        <v>0.801233087813375</v>
       </c>
       <c r="L42">
-        <v>0.8060856582100233</v>
+        <v>0.8278567943027546</v>
       </c>
       <c r="M42">
-        <v>0.8328871819944875</v>
+        <v>0.8602244901361188</v>
       </c>
       <c r="N42">
-        <v>0.8628478223642969</v>
+        <v>0.8988211118199823</v>
       </c>
       <c r="O42">
-        <v>0.8761134836462897</v>
+        <v>0.9140642323866298</v>
       </c>
       <c r="P42">
-        <v>0.8840140112671931</v>
+        <v>0.9238112124598866</v>
+      </c>
+      <c r="Q42">
+        <v>0.9421875052251131</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.556349299990362</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.5845858200983682</v>
+        <v>0.5367876025581952</v>
       </c>
       <c r="D43">
-        <v>0.6281925604511666</v>
+        <v>0.5884417844953449</v>
       </c>
       <c r="E43">
-        <v>0.6474645222138913</v>
+        <v>0.6305007761357251</v>
       </c>
       <c r="F43">
-        <v>0.6658508164698665</v>
+        <v>0.6584672915381926</v>
       </c>
       <c r="G43">
-        <v>0.6953729801895252</v>
+        <v>0.7381319882969115</v>
       </c>
       <c r="H43">
-        <v>0.7165363894541938</v>
+        <v>0.7702906447930022</v>
       </c>
       <c r="I43">
-        <v>0.7287428517150074</v>
+        <v>0.7957327656500345</v>
       </c>
       <c r="J43">
-        <v>0.7635126472630993</v>
+        <v>0.8141583416535845</v>
       </c>
       <c r="K43">
-        <v>0.7766894445307863</v>
+        <v>0.8429863458373563</v>
       </c>
       <c r="L43">
-        <v>0.782018497856882</v>
+        <v>0.8704525884709612</v>
       </c>
       <c r="M43">
-        <v>0.811204774603369</v>
+        <v>0.8858219590742571</v>
       </c>
       <c r="N43">
-        <v>0.828298328223347</v>
+        <v>0.9014980028079265</v>
       </c>
       <c r="O43">
-        <v>0.8466015729659361</v>
+        <v>0.9110978161304012</v>
       </c>
       <c r="P43">
-        <v>0.866029547922833</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.531142077332986</v>
-      </c>
-      <c r="C44">
-        <v>0.5534661866022449</v>
-      </c>
-      <c r="D44">
-        <v>0.56698701370099</v>
-      </c>
-      <c r="E44">
-        <v>0.620031778981365</v>
-      </c>
-      <c r="F44">
-        <v>0.6594245855709158</v>
-      </c>
-      <c r="G44">
-        <v>0.6909765771796053</v>
-      </c>
-      <c r="H44">
-        <v>0.7133001550590943</v>
-      </c>
-      <c r="I44">
-        <v>0.7323003253819161</v>
-      </c>
-      <c r="J44">
-        <v>0.7528935564384555</v>
-      </c>
-      <c r="K44">
-        <v>0.7724191995604216</v>
-      </c>
-      <c r="L44">
-        <v>0.7930854445257278</v>
-      </c>
-      <c r="M44">
-        <v>0.8190442501469444</v>
-      </c>
-      <c r="N44">
-        <v>0.8532169003610808</v>
-      </c>
-      <c r="O44">
-        <v>0.8766378977418169</v>
-      </c>
-      <c r="P44">
-        <v>0.893204761640541</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.523028316214328</v>
-      </c>
-      <c r="C45">
-        <v>0.5778310138275996</v>
-      </c>
-      <c r="D45">
-        <v>0.6199097189934275</v>
-      </c>
-      <c r="E45">
-        <v>0.6733652558540062</v>
-      </c>
-      <c r="F45">
-        <v>0.7225831599567458</v>
-      </c>
-      <c r="G45">
-        <v>0.7532819788865696</v>
-      </c>
-      <c r="H45">
-        <v>0.7864096176910289</v>
-      </c>
-      <c r="I45">
-        <v>0.8077801568330422</v>
-      </c>
-      <c r="J45">
-        <v>0.8239796265922745</v>
-      </c>
-      <c r="K45">
-        <v>0.8427766467483349</v>
-      </c>
-      <c r="L45">
-        <v>0.8687206319824909</v>
-      </c>
-      <c r="M45">
-        <v>0.8954189132756132</v>
-      </c>
-      <c r="N45">
-        <v>0.9132506057882768</v>
-      </c>
-      <c r="O45">
-        <v>0.9289566971746739</v>
-      </c>
-      <c r="P45">
-        <v>0.9378009314809052</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.4367333784920707</v>
-      </c>
-      <c r="C46">
-        <v>0.5425429154744063</v>
-      </c>
-      <c r="D46">
-        <v>0.5771025558699054</v>
-      </c>
-      <c r="E46">
-        <v>0.6392933696490982</v>
-      </c>
-      <c r="F46">
-        <v>0.6857360884758095</v>
-      </c>
-      <c r="G46">
-        <v>0.7092763137276223</v>
-      </c>
-      <c r="H46">
-        <v>0.7344243403473428</v>
-      </c>
-      <c r="I46">
-        <v>0.747344570129066</v>
-      </c>
-      <c r="J46">
-        <v>0.801233087813375</v>
-      </c>
-      <c r="K46">
-        <v>0.8278567943027546</v>
-      </c>
-      <c r="L46">
-        <v>0.8602244901361188</v>
-      </c>
-      <c r="M46">
-        <v>0.8988211118199823</v>
-      </c>
-      <c r="N46">
-        <v>0.9140642323866298</v>
-      </c>
-      <c r="O46">
-        <v>0.9238112124598866</v>
-      </c>
-      <c r="P46">
-        <v>0.9421875052251131</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.5367876025581952</v>
-      </c>
-      <c r="C47">
-        <v>0.5884417844953449</v>
-      </c>
-      <c r="D47">
-        <v>0.6305007761357251</v>
-      </c>
-      <c r="E47">
-        <v>0.6584672915381926</v>
-      </c>
-      <c r="F47">
-        <v>0.7381319882969115</v>
-      </c>
-      <c r="G47">
-        <v>0.7702906447930022</v>
-      </c>
-      <c r="H47">
-        <v>0.7957327656500345</v>
-      </c>
-      <c r="I47">
-        <v>0.8141583416535845</v>
-      </c>
-      <c r="J47">
-        <v>0.8429863458373563</v>
-      </c>
-      <c r="K47">
-        <v>0.8704525884709612</v>
-      </c>
-      <c r="L47">
-        <v>0.8858219590742571</v>
-      </c>
-      <c r="M47">
-        <v>0.9014980028079265</v>
-      </c>
-      <c r="N47">
-        <v>0.9110978161304012</v>
-      </c>
-      <c r="O47">
         <v>0.9257248681485399</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.9436327394339777</v>
       </c>
     </row>
